--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -442,7 +442,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.720955800193191</v>
+        <v>4.766270954987323</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.448012329545969</v>
+        <v>3.42868537831944</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.843133091484296</v>
+        <v>3.894525960227657</v>
       </c>
     </row>
     <row r="4">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.65217391304348</v>
+        <v>95.68965517241379</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>64.34782608695652</v>
+        <v>64.65517241379311</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.347826086956522</v>
+        <v>4.310344827586207</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35.65217391304348</v>
+        <v>35.3448275862069</v>
       </c>
     </row>
     <row r="6">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.718909090909092</v>
+        <v>3.696486486486487</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.20774600360396</v>
+        <v>12.17800676700963</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791787493767707</v>
+        <v>-8.791782359687629</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54462412563478</v>
+        <v>38.54459413790421</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02741339540493</v>
+        <v>-32.02739802562728</v>
       </c>
     </row>
     <row r="10">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.720955800193191</v>
+        <v>4.766270954987323</v>
       </c>
     </row>
     <row r="11">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.983943837120484</v>
+        <v>3.972276416934467</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.45428494013697</v>
+        <v>13.40454352252829</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.638684739182456</v>
+        <v>2.651927277101982</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.0217036217385676</v>
+        <v>-0.03153827838289425</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.54330321288962</v>
+        <v>8.629009524988723</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.147212041724103</v>
+        <v>0.1667139613486102</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8834156315349508</v>
+        <v>0.8810417533861374</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.350888644115867</v>
+        <v>0.355571299162624</v>
       </c>
     </row>
     <row r="15">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.58478488287689</v>
+        <v>14.56591488300176</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6671086457840698</v>
+        <v>0.6764342599160132</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.25806451612905</v>
+        <v>94.54147465437789</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.506144831481828</v>
+        <v>2.533825421920513</v>
       </c>
     </row>
   </sheetData>
@@ -708,7 +708,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
+          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -472,7 +472,7 @@
         <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.766270954987323</v>
+        <v>4.766271550373824</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>3.42868537831944</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.894525960227657</v>
+        <v>3.894525878804123</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>3.696486486486487</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.17800676700963</v>
+        <v>12.17801071817231</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791782359687629</v>
+        <v>-8.791787902916088</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54459413790421</v>
+        <v>38.54458842745316</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02739802562728</v>
+        <v>-32.02740756754329</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         <v>3.499741379310346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.766270954987323</v>
+        <v>4.766271550373824</v>
       </c>
     </row>
     <row r="11">
@@ -589,7 +589,7 @@
         <v>3.972276416934467</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.40454352252829</v>
+        <v>13.40454892611204</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +602,7 @@
         <v>2.651927277101982</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03153827838289425</v>
+        <v>-0.03153799374004402</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>8.629009524988723</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1667139613486102</v>
+        <v>0.1667112763682104</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>0.8810417533861374</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.355571299162624</v>
+        <v>0.355571200243011</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         <v>14.56591488300176</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6764342599160132</v>
+        <v>0.6764341416878362</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         <v>94.54147465437789</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.533825421920513</v>
+        <v>2.533824646442687</v>
       </c>
     </row>
   </sheetData>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -472,7 +472,7 @@
         <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.766271550373824</v>
+        <v>4.766271304346992</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         <v>3.696486486486487</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.17801071817231</v>
+        <v>12.17801022895345</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791787902916088</v>
+        <v>-8.791787704079452</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54458842745316</v>
+        <v>38.54460488262499</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02740756754329</v>
+        <v>-32.02741683447206</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         <v>3.499741379310346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.766271550373824</v>
+        <v>4.766271304346992</v>
       </c>
     </row>
     <row r="11">
@@ -589,7 +589,7 @@
         <v>3.972276416934467</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.40454892611204</v>
+        <v>13.4045464149397</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +602,7 @@
         <v>2.651927277101982</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03153799374004402</v>
+        <v>-0.03153888819748991</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>8.629009524988723</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1667112763682104</v>
+        <v>0.1667138987122159</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>0.8810417533861374</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.355571200243011</v>
+        <v>0.3555712485007971</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         <v>14.56591488300176</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6764341416878362</v>
+        <v>0.6764340386298822</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         <v>94.54147465437789</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.533824646442687</v>
+        <v>2.533824601958516</v>
       </c>
     </row>
   </sheetData>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -442,7 +442,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.766271304346992</v>
+        <v>4.755945312720088</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.42868537831944</v>
+        <v>3.408469136214709</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.894525878804123</v>
+        <v>3.891645733695004</v>
       </c>
     </row>
     <row r="4">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.68965517241379</v>
+        <v>95.72649572649573</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>64.65517241379311</v>
+        <v>64.95726495726495</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.310344827586207</v>
+        <v>4.273504273504273</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35.3448275862069</v>
+        <v>35.04273504273504</v>
       </c>
     </row>
     <row r="6">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.696486486486487</v>
+        <v>3.673214285714287</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.17801022895345</v>
+        <v>12.06459141507334</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791787704079452</v>
+        <v>-8.791788925788385</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54460488262499</v>
+        <v>38.54463275870208</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02741683447206</v>
+        <v>-32.02742385341527</v>
       </c>
     </row>
     <row r="10">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.766271304346992</v>
+        <v>4.755945312720088</v>
       </c>
     </row>
     <row r="11">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.972276416934467</v>
+        <v>3.961386811469624</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.4045464149397</v>
+        <v>13.34711369180711</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.651927277101982</v>
+        <v>2.664304280248351</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03153888819748991</v>
+        <v>-0.02931179138729888</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.629009524988723</v>
+        <v>8.710085873783012</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1667138987122159</v>
+        <v>0.1936187715291005</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8810417533861374</v>
+        <v>0.8782644727023218</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3555712485007971</v>
+        <v>0.3563276242742608</v>
       </c>
     </row>
     <row r="15">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.56591488300176</v>
+        <v>14.54247474070697</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6764340386298822</v>
+        <v>0.6778716925034239</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.54147465437789</v>
+        <v>94.79262672811062</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.533824601958516</v>
+        <v>2.543695379374659</v>
       </c>
     </row>
   </sheetData>
@@ -708,7 +708,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
+          <t>Jan 2017 to Sept 2026; 117 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -442,7 +442,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         <v>3.479145299145301</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.755945312720088</v>
+        <v>4.755945221301799</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>3.408469136214709</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.891645733695004</v>
+        <v>3.891645895145746</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>3.673214285714287</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.06459141507334</v>
+        <v>12.06459049542588</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791788925788385</v>
+        <v>-8.791787481952579</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54463275870208</v>
+        <v>38.54463634027958</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02742385341527</v>
+        <v>-32.0273955026533</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         <v>3.479145299145301</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.755945312720088</v>
+        <v>4.755945221301799</v>
       </c>
     </row>
     <row r="11">
@@ -589,7 +589,7 @@
         <v>3.961386811469624</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.34711369180711</v>
+        <v>13.34711191641553</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +602,7 @@
         <v>2.664304280248351</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.02931179138729888</v>
+        <v>-0.02931161959291562</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>8.710085873783012</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1936187715291005</v>
+        <v>0.1936184987708893</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>0.8782644727023218</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3563276242742608</v>
+        <v>0.3563276648225666</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         <v>14.54247474070697</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6778716925034239</v>
+        <v>0.67787179075673</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         <v>94.79262672811062</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.543695379374659</v>
+        <v>2.543695603216068</v>
       </c>
     </row>
   </sheetData>

--- a/isolated_excel/Table 4 - Current Update.xlsx
+++ b/isolated_excel/Table 4 - Current Update.xlsx
@@ -442,7 +442,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         <v>3.479145299145301</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.755945221301799</v>
+        <v>4.755945176363778</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         <v>3.673214285714287</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.06459049542588</v>
+        <v>12.06458916745936</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791787481952579</v>
+        <v>-8.791785148593888</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54463634027958</v>
+        <v>38.54463275870208</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.0273955026533</v>
+        <v>-32.02740504457099</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         <v>3.479145299145301</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.755945221301799</v>
+        <v>4.755945176363778</v>
       </c>
     </row>
     <row r="11">
@@ -589,7 +589,7 @@
         <v>3.961386811469624</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.34711191641553</v>
+        <v>13.34711112720858</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +602,7 @@
         <v>2.664304280248351</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.02931161959291562</v>
+        <v>-0.02931237411583189</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>8.710085873783012</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1936184987708893</v>
+        <v>0.1936187840194536</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>0.8782644727023218</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3563276648225666</v>
+        <v>0.3563276825251428</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         <v>14.54247474070697</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.67787179075673</v>
+        <v>0.6778716976776478</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         <v>94.79262672811062</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.543695603216068</v>
+        <v>2.543695998330112</v>
       </c>
     </row>
   </sheetData>
